--- a/import_kemo_converted.xlsx
+++ b/import_kemo_converted.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trenaldyikkyuarifin/Documents/Project WEB/ahcc-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABDE0F76-48D7-B841-8A34-F3347D4DBEA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{077AC079-5E77-0248-B9B6-5FD4AD2CA98E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1480" yWindow="1680" windowWidth="27240" windowHeight="16320" xr2:uid="{E3E8F785-9F5E-9C4B-BB50-7A6474A568F3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="371">
   <si>
     <t>no_rm</t>
   </si>
@@ -1046,10 +1046,110 @@
     <t>Glioblastoma</t>
   </si>
   <si>
-    <t>t</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sani Al Santi, Ny </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yosi Erawati, Ny </t>
+  </si>
+  <si>
+    <t>087737373783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ca Cervix </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Utami Listiowati , Ny </t>
+  </si>
+  <si>
+    <t>081230206599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ca mamae </t>
+  </si>
+  <si>
+    <t>Ema Sumiarti, Ny</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 08123131727</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Agustinus Atan Matunaga, Tn
+  </t>
+  </si>
+  <si>
+    <t>081803222958</t>
+  </si>
+  <si>
+    <t>PLL</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Anik, Ny</t>
+  </si>
+  <si>
+    <t>Ca cx</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Endang Tri Silowati , Ny</t>
+  </si>
+  <si>
+    <t>081231022879</t>
+  </si>
+  <si>
+    <t>Ong Tony, Tn</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 085100160555</t>
+  </si>
+  <si>
+    <t>MM</t>
+  </si>
+  <si>
+    <t>Musyarafah, Ny</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 087773437373 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Aini Rusdiyati, Ny</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 082234347789</t>
+  </si>
+  <si>
+    <t>Sicilia, Nn</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 5340704</t>
+  </si>
+  <si>
+    <t>Ca mamae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lila Tri Ermanova, Ny </t>
+  </si>
+  <si>
+    <t>Soehardjo Partowidjojo, Tn</t>
+  </si>
+  <si>
+    <t>Liauw Debie Sintawati, Ny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jauw Yustinus Yanaprasetya, Tn </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 08123291688</t>
+  </si>
+  <si>
+    <t>Digestives</t>
+  </si>
+  <si>
+    <t>Lie Lie Lan, Ny</t>
+  </si>
+  <si>
+    <t>0816516648</t>
+  </si>
+  <si>
+    <t>Ca Buli</t>
   </si>
 </sst>
 </file>
@@ -1422,7 +1522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ADF526F-403E-7045-8C88-98DA93361EEC}">
-  <dimension ref="A1:J182"/>
+  <dimension ref="A1:J197"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="7" max="7" width="15.1640625" bestFit="1" customWidth="1"/>
@@ -7215,11 +7315,11 @@
       <c r="A182">
         <v>427286</v>
       </c>
-      <c r="B182" s="1" t="s">
+      <c r="B182" s="1">
+        <v>46014</v>
+      </c>
+      <c r="C182" t="s">
         <v>336</v>
-      </c>
-      <c r="C182" t="s">
-        <v>337</v>
       </c>
       <c r="D182">
         <v>0</v>
@@ -7241,6 +7341,474 @@
       </c>
       <c r="J182" t="s">
         <v>58</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A183">
+        <v>422899</v>
+      </c>
+      <c r="B183" s="1">
+        <v>46024</v>
+      </c>
+      <c r="C183" t="s">
+        <v>337</v>
+      </c>
+      <c r="D183">
+        <v>0</v>
+      </c>
+      <c r="E183">
+        <v>1</v>
+      </c>
+      <c r="F183" t="s">
+        <v>11</v>
+      </c>
+      <c r="G183" t="s">
+        <v>338</v>
+      </c>
+      <c r="H183" t="s">
+        <v>339</v>
+      </c>
+      <c r="I183" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J183" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A184">
+        <v>427705</v>
+      </c>
+      <c r="B184" s="1">
+        <v>46027</v>
+      </c>
+      <c r="C184" t="s">
+        <v>340</v>
+      </c>
+      <c r="D184">
+        <v>0</v>
+      </c>
+      <c r="E184">
+        <v>1</v>
+      </c>
+      <c r="F184" t="s">
+        <v>11</v>
+      </c>
+      <c r="G184" t="s">
+        <v>341</v>
+      </c>
+      <c r="H184" t="s">
+        <v>342</v>
+      </c>
+      <c r="I184" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J184" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A185">
+        <v>394755</v>
+      </c>
+      <c r="B185" s="1">
+        <v>46030</v>
+      </c>
+      <c r="C185" t="s">
+        <v>343</v>
+      </c>
+      <c r="D185">
+        <v>0</v>
+      </c>
+      <c r="E185">
+        <v>1</v>
+      </c>
+      <c r="F185" t="s">
+        <v>11</v>
+      </c>
+      <c r="G185" t="s">
+        <v>344</v>
+      </c>
+      <c r="H185" t="s">
+        <v>74</v>
+      </c>
+      <c r="I185" t="s">
+        <v>53</v>
+      </c>
+      <c r="J185" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A186">
+        <v>428052</v>
+      </c>
+      <c r="B186" s="1">
+        <v>46031</v>
+      </c>
+      <c r="C186" t="s">
+        <v>345</v>
+      </c>
+      <c r="D186">
+        <v>0</v>
+      </c>
+      <c r="E186">
+        <v>1</v>
+      </c>
+      <c r="F186" t="s">
+        <v>11</v>
+      </c>
+      <c r="G186" t="s">
+        <v>346</v>
+      </c>
+      <c r="H186" t="s">
+        <v>347</v>
+      </c>
+      <c r="I186" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J186" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A187">
+        <v>313352</v>
+      </c>
+      <c r="B187" s="1">
+        <v>46034</v>
+      </c>
+      <c r="C187" t="s">
+        <v>348</v>
+      </c>
+      <c r="D187">
+        <v>0</v>
+      </c>
+      <c r="E187">
+        <v>1</v>
+      </c>
+      <c r="F187" t="s">
+        <v>11</v>
+      </c>
+      <c r="G187" t="s">
+        <v>245</v>
+      </c>
+      <c r="H187" t="s">
+        <v>349</v>
+      </c>
+      <c r="I187" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J187" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A188">
+        <v>428249</v>
+      </c>
+      <c r="B188" s="1">
+        <v>46034</v>
+      </c>
+      <c r="C188" t="s">
+        <v>350</v>
+      </c>
+      <c r="D188">
+        <v>0</v>
+      </c>
+      <c r="E188">
+        <v>1</v>
+      </c>
+      <c r="F188" t="s">
+        <v>11</v>
+      </c>
+      <c r="G188" t="s">
+        <v>351</v>
+      </c>
+      <c r="H188" t="s">
+        <v>349</v>
+      </c>
+      <c r="I188" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J188" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A189">
+        <v>428212</v>
+      </c>
+      <c r="B189" s="1">
+        <v>46034</v>
+      </c>
+      <c r="C189" t="s">
+        <v>352</v>
+      </c>
+      <c r="D189">
+        <v>0</v>
+      </c>
+      <c r="E189">
+        <v>1</v>
+      </c>
+      <c r="F189" t="s">
+        <v>11</v>
+      </c>
+      <c r="G189" t="s">
+        <v>353</v>
+      </c>
+      <c r="H189" t="s">
+        <v>354</v>
+      </c>
+      <c r="I189" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J189" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A190">
+        <v>53707</v>
+      </c>
+      <c r="B190" s="1">
+        <v>46036</v>
+      </c>
+      <c r="C190" t="s">
+        <v>355</v>
+      </c>
+      <c r="D190">
+        <v>0</v>
+      </c>
+      <c r="E190">
+        <v>1</v>
+      </c>
+      <c r="F190" t="s">
+        <v>11</v>
+      </c>
+      <c r="G190" t="s">
+        <v>356</v>
+      </c>
+      <c r="H190" t="s">
+        <v>349</v>
+      </c>
+      <c r="I190" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J190" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A191">
+        <v>427806</v>
+      </c>
+      <c r="B191" s="1">
+        <v>46043</v>
+      </c>
+      <c r="C191" t="s">
+        <v>357</v>
+      </c>
+      <c r="D191">
+        <v>0</v>
+      </c>
+      <c r="E191">
+        <v>1</v>
+      </c>
+      <c r="F191" t="s">
+        <v>11</v>
+      </c>
+      <c r="G191" t="s">
+        <v>358</v>
+      </c>
+      <c r="H191" t="s">
+        <v>339</v>
+      </c>
+      <c r="I191" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J191" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A192">
+        <v>336282</v>
+      </c>
+      <c r="B192" s="1">
+        <v>46044</v>
+      </c>
+      <c r="C192" t="s">
+        <v>359</v>
+      </c>
+      <c r="D192">
+        <v>0</v>
+      </c>
+      <c r="E192">
+        <v>1</v>
+      </c>
+      <c r="F192" t="s">
+        <v>11</v>
+      </c>
+      <c r="G192" t="s">
+        <v>360</v>
+      </c>
+      <c r="H192" t="s">
+        <v>361</v>
+      </c>
+      <c r="I192" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J192" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="193" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A193">
+        <v>428095</v>
+      </c>
+      <c r="B193" s="1">
+        <v>46057</v>
+      </c>
+      <c r="C193" t="s">
+        <v>362</v>
+      </c>
+      <c r="D193">
+        <v>0</v>
+      </c>
+      <c r="E193">
+        <v>1</v>
+      </c>
+      <c r="F193" t="s">
+        <v>11</v>
+      </c>
+      <c r="H193" t="s">
+        <v>52</v>
+      </c>
+      <c r="I193" t="s">
+        <v>53</v>
+      </c>
+      <c r="J193" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A194">
+        <v>428744</v>
+      </c>
+      <c r="B194" s="1">
+        <v>46059</v>
+      </c>
+      <c r="C194" t="s">
+        <v>363</v>
+      </c>
+      <c r="D194">
+        <v>0</v>
+      </c>
+      <c r="E194">
+        <v>1</v>
+      </c>
+      <c r="F194" t="s">
+        <v>11</v>
+      </c>
+      <c r="I194" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J194" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A195">
+        <v>363441</v>
+      </c>
+      <c r="B195" s="1">
+        <v>46062</v>
+      </c>
+      <c r="C195" t="s">
+        <v>364</v>
+      </c>
+      <c r="D195">
+        <v>0</v>
+      </c>
+      <c r="E195">
+        <v>1</v>
+      </c>
+      <c r="F195" t="s">
+        <v>11</v>
+      </c>
+      <c r="H195" t="s">
+        <v>98</v>
+      </c>
+      <c r="I195" t="s">
+        <v>53</v>
+      </c>
+      <c r="J195" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A196">
+        <v>429120</v>
+      </c>
+      <c r="B196" s="1">
+        <v>46072</v>
+      </c>
+      <c r="C196" t="s">
+        <v>365</v>
+      </c>
+      <c r="D196">
+        <v>0</v>
+      </c>
+      <c r="E196">
+        <v>1</v>
+      </c>
+      <c r="F196" t="s">
+        <v>11</v>
+      </c>
+      <c r="G196" t="s">
+        <v>366</v>
+      </c>
+      <c r="H196" t="s">
+        <v>286</v>
+      </c>
+      <c r="I196" t="s">
+        <v>367</v>
+      </c>
+      <c r="J196" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A197">
+        <v>299196</v>
+      </c>
+      <c r="B197" s="1">
+        <v>46077</v>
+      </c>
+      <c r="C197" t="s">
+        <v>368</v>
+      </c>
+      <c r="D197">
+        <v>0</v>
+      </c>
+      <c r="E197">
+        <v>1</v>
+      </c>
+      <c r="F197" t="s">
+        <v>11</v>
+      </c>
+      <c r="G197" t="s">
+        <v>369</v>
+      </c>
+      <c r="H197" t="s">
+        <v>370</v>
+      </c>
+      <c r="I197" t="s">
+        <v>28</v>
+      </c>
+      <c r="J197" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>
